--- a/artfynd/A 43740-2024 artfynd.xlsx
+++ b/artfynd/A 43740-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150774</v>
+        <v>121150772</v>
       </c>
       <c r="B2" t="n">
-        <v>78334</v>
+        <v>79190</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150772</v>
+        <v>121150774</v>
       </c>
       <c r="B3" t="n">
-        <v>79187</v>
+        <v>78337</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -900,7 +900,7 @@
         <v>121150773</v>
       </c>
       <c r="B4" t="n">
-        <v>78335</v>
+        <v>78338</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>

--- a/artfynd/A 43740-2024 artfynd.xlsx
+++ b/artfynd/A 43740-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150772</v>
+        <v>121150773</v>
       </c>
       <c r="B2" t="n">
-        <v>79190</v>
+        <v>78338</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150773</v>
+        <v>121150772</v>
       </c>
       <c r="B4" t="n">
-        <v>78338</v>
+        <v>79190</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 43740-2024 artfynd.xlsx
+++ b/artfynd/A 43740-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150773</v>
+        <v>121150772</v>
       </c>
       <c r="B2" t="n">
-        <v>78338</v>
+        <v>79193</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -789,7 +789,7 @@
         <v>121150774</v>
       </c>
       <c r="B3" t="n">
-        <v>78337</v>
+        <v>78340</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150772</v>
+        <v>121150773</v>
       </c>
       <c r="B4" t="n">
-        <v>79190</v>
+        <v>78341</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 43740-2024 artfynd.xlsx
+++ b/artfynd/A 43740-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150772</v>
+        <v>121150774</v>
       </c>
       <c r="B2" t="n">
-        <v>79193</v>
+        <v>78340</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>6446</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150774</v>
+        <v>121150772</v>
       </c>
       <c r="B3" t="n">
-        <v>78340</v>
+        <v>79193</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">

--- a/artfynd/A 43740-2024 artfynd.xlsx
+++ b/artfynd/A 43740-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150774</v>
+        <v>121150772</v>
       </c>
       <c r="B2" t="n">
-        <v>78340</v>
+        <v>79196</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>6446</v>
+        <v>229821</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Carbonicola anthracophila</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Nyl.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150772</v>
+        <v>121150773</v>
       </c>
       <c r="B3" t="n">
-        <v>79193</v>
+        <v>78344</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -897,10 +897,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>121150773</v>
+        <v>121150774</v>
       </c>
       <c r="B4" t="n">
-        <v>78341</v>
+        <v>78343</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -913,21 +913,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>228912</v>
+        <v>6446</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Kolflarnlav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Carbonicola anthracophila</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Nyl.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">

--- a/artfynd/A 43740-2024 artfynd.xlsx
+++ b/artfynd/A 43740-2024 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>121150772</v>
+        <v>121150773</v>
       </c>
       <c r="B2" t="n">
-        <v>79196</v>
+        <v>78344</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -691,21 +691,21 @@
         </is>
       </c>
       <c r="E2" t="n">
-        <v>229821</v>
+        <v>228912</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Vedflamlav</t>
+          <t>Mörk kolflarnlav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Ramboldia elabens</t>
+          <t>Carbonicola myrmecina</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Fr.) Kantvilas &amp; Elix</t>
+          <t>(Ach.) Bendiksby &amp; Timdal</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -786,10 +786,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>121150773</v>
+        <v>121150772</v>
       </c>
       <c r="B3" t="n">
-        <v>78344</v>
+        <v>79196</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -802,21 +802,21 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>228912</v>
+        <v>229821</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Mörk kolflarnlav</t>
+          <t>Vedflamlav</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Carbonicola myrmecina</t>
+          <t>Ramboldia elabens</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.) Bendiksby &amp; Timdal</t>
+          <t>(Fr.) Kantvilas &amp; Elix</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
